--- a/data/profiles/minimal_1547.xlsx
+++ b/data/profiles/minimal_1547.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ande882/projects/ieee-std-1815-2-test-tool/data/profiles/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915CA1A1-8A46-9047-ACEE-A6D7D7E72A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="580" windowWidth="16100" windowHeight="9660" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Key" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,7 @@
     <sheet name="CTR" sheetId="6" r:id="rId6"/>
     <sheet name="System Diagrams" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1758,8 +1764,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1796,13 +1802,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1840,7 +1854,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1874,6 +1888,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1908,9 +1923,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2083,17 +2099,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="I2:S50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="9:19">
+    <row r="2" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="9:19"/>
-    <row r="4" spans="9:19">
+    <row r="4" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I4" t="s">
         <v>1</v>
       </c>
@@ -2116,12 +2131,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="9:19">
+    <row r="5" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="9:19">
+    <row r="6" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I6" t="s">
         <v>9</v>
       </c>
@@ -2144,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="9:19">
+    <row r="7" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I7" t="s">
         <v>10</v>
       </c>
@@ -2170,7 +2185,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="9:19">
+    <row r="8" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I8" t="s">
         <v>12</v>
       </c>
@@ -2199,7 +2214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="9:19">
+    <row r="9" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I9" t="s">
         <v>15</v>
       </c>
@@ -2222,7 +2237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="9:19">
+    <row r="10" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I10" t="s">
         <v>16</v>
       </c>
@@ -2245,7 +2260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="9:19">
+    <row r="11" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I11" t="s">
         <v>17</v>
       </c>
@@ -2268,13 +2283,12 @@
         <v>586</v>
       </c>
     </row>
-    <row r="12" spans="9:19"/>
-    <row r="13" spans="9:19">
+    <row r="13" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="9:19">
+    <row r="14" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I14" t="s">
         <v>21</v>
       </c>
@@ -2300,7 +2314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="9:19">
+    <row r="15" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I15" t="s">
         <v>24</v>
       </c>
@@ -2317,7 +2331,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="16" spans="9:19">
+    <row r="16" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I16" t="s">
         <v>26</v>
       </c>
@@ -2340,7 +2354,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="17" spans="9:19">
+    <row r="17" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I17" t="s">
         <v>28</v>
       </c>
@@ -2363,7 +2377,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="9:19">
+    <row r="18" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I18" t="s">
         <v>30</v>
       </c>
@@ -2374,8 +2388,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="19" spans="9:19"/>
-    <row r="20" spans="9:19">
+    <row r="20" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I20" t="s">
         <v>31</v>
       </c>
@@ -2398,7 +2411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="9:19">
+    <row r="21" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I21" t="s">
         <v>33</v>
       </c>
@@ -2430,7 +2443,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="9:19">
+    <row r="22" spans="9:19" x14ac:dyDescent="0.2">
       <c r="J22" t="s">
         <v>36</v>
       </c>
@@ -2450,7 +2463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="9:19">
+    <row r="23" spans="9:19" x14ac:dyDescent="0.2">
       <c r="J23" t="s">
         <v>37</v>
       </c>
@@ -2470,7 +2483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="9:19">
+    <row r="24" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I24" t="s">
         <v>38</v>
       </c>
@@ -2499,7 +2512,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="9:19">
+    <row r="25" spans="9:19" x14ac:dyDescent="0.2">
       <c r="J25" t="s">
         <v>41</v>
       </c>
@@ -2519,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="9:19">
+    <row r="26" spans="9:19" x14ac:dyDescent="0.2">
       <c r="J26" t="s">
         <v>42</v>
       </c>
@@ -2536,7 +2549,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="27" spans="9:19">
+    <row r="27" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I27" t="s">
         <v>43</v>
       </c>
@@ -2565,7 +2578,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="9:19">
+    <row r="28" spans="9:19" x14ac:dyDescent="0.2">
       <c r="J28" t="s">
         <v>46</v>
       </c>
@@ -2585,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="9:19">
+    <row r="29" spans="9:19" x14ac:dyDescent="0.2">
       <c r="J29" t="s">
         <v>47</v>
       </c>
@@ -2602,7 +2615,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="9:19">
+    <row r="30" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I30" t="s">
         <v>48</v>
       </c>
@@ -2631,7 +2644,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="9:19">
+    <row r="31" spans="9:19" x14ac:dyDescent="0.2">
       <c r="J31" t="s">
         <v>51</v>
       </c>
@@ -2654,7 +2667,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="9:19">
+    <row r="32" spans="9:19" x14ac:dyDescent="0.2">
       <c r="J32" t="s">
         <v>53</v>
       </c>
@@ -2671,7 +2684,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="9:19">
+    <row r="33" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I33" t="s">
         <v>54</v>
       </c>
@@ -2682,7 +2695,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="34" spans="9:19">
+    <row r="34" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I34" t="s">
         <v>56</v>
       </c>
@@ -2705,7 +2718,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="9:19">
+    <row r="35" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I35" t="s">
         <v>58</v>
       </c>
@@ -2725,7 +2738,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="9:19">
+    <row r="36" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I36" t="s">
         <v>62</v>
       </c>
@@ -2733,8 +2746,7 @@
         <v>65535</v>
       </c>
     </row>
-    <row r="37" spans="9:19"/>
-    <row r="38" spans="9:19">
+    <row r="38" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I38" t="s">
         <v>63</v>
       </c>
@@ -2745,7 +2757,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="9:19">
+    <row r="39" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I39" t="s">
         <v>66</v>
       </c>
@@ -2756,7 +2768,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="9:19">
+    <row r="40" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I40" t="s">
         <v>69</v>
       </c>
@@ -2767,7 +2779,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="9:19">
+    <row r="41" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I41" t="s">
         <v>72</v>
       </c>
@@ -2778,8 +2790,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="9:19"/>
-    <row r="43" spans="9:19">
+    <row r="43" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I43" t="s">
         <v>75</v>
       </c>
@@ -2790,7 +2801,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="9:19">
+    <row r="44" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I44" t="s">
         <v>77</v>
       </c>
@@ -2801,7 +2812,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="9:19">
+    <row r="45" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I45" t="s">
         <v>79</v>
       </c>
@@ -2812,7 +2823,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="9:19">
+    <row r="46" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I46" t="s">
         <v>81</v>
       </c>
@@ -2823,8 +2834,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="9:19"/>
-    <row r="48" spans="9:19">
+    <row r="48" spans="9:19" x14ac:dyDescent="0.2">
       <c r="I48" t="s">
         <v>83</v>
       </c>
@@ -2835,7 +2845,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="9:13">
+    <row r="49" spans="9:13" x14ac:dyDescent="0.2">
       <c r="I49" t="s">
         <v>85</v>
       </c>
@@ -2846,7 +2856,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="50" spans="9:13">
+    <row r="50" spans="9:13" x14ac:dyDescent="0.2">
       <c r="I50" t="s">
         <v>87</v>
       </c>
@@ -2863,11 +2873,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>89</v>
       </c>
@@ -2890,7 +2900,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E2" t="s">
         <v>96</v>
       </c>
@@ -2910,7 +2920,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -2939,7 +2949,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>110</v>
       </c>
@@ -2968,7 +2978,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -2997,7 +3007,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>123</v>
       </c>
@@ -3026,7 +3036,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -3055,7 +3065,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>133</v>
       </c>
@@ -3084,7 +3094,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>138</v>
       </c>
@@ -3119,11 +3129,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -3149,7 +3159,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="F2" t="s">
         <v>96</v>
       </c>
@@ -3169,7 +3179,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>145</v>
       </c>
@@ -3198,7 +3208,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -3227,7 +3237,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>156</v>
       </c>
@@ -3256,7 +3266,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -3285,7 +3295,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>166</v>
       </c>
@@ -3314,7 +3324,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>172</v>
       </c>
@@ -3343,7 +3353,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>176</v>
       </c>
@@ -3372,7 +3382,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>180</v>
       </c>
@@ -3401,7 +3411,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>183</v>
       </c>
@@ -3430,7 +3440,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>186</v>
       </c>
@@ -3459,7 +3469,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>189</v>
       </c>
@@ -3488,7 +3498,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>192</v>
       </c>
@@ -3517,7 +3527,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>195</v>
       </c>
@@ -3546,7 +3556,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -3578,7 +3588,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -3610,7 +3620,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>126</v>
       </c>
@@ -3642,7 +3652,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>131</v>
       </c>
@@ -3674,7 +3684,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>136</v>
       </c>
@@ -3706,7 +3716,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>206</v>
       </c>
@@ -3744,11 +3754,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>89</v>
       </c>
@@ -3774,7 +3784,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>213</v>
       </c>
@@ -3812,7 +3822,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>221</v>
       </c>
@@ -3850,7 +3860,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>227</v>
       </c>
@@ -3888,7 +3898,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>231</v>
       </c>
@@ -3926,7 +3936,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>235</v>
       </c>
@@ -3964,7 +3974,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>239</v>
       </c>
@@ -4002,7 +4012,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>243</v>
       </c>
@@ -4040,7 +4050,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>247</v>
       </c>
@@ -4054,7 +4064,7 @@
         <v>70000</v>
       </c>
       <c r="E9">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -4078,7 +4088,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>252</v>
       </c>
@@ -4092,7 +4102,7 @@
         <v>2147483647</v>
       </c>
       <c r="E10">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -4116,7 +4126,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>258</v>
       </c>
@@ -4130,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -4154,7 +4164,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>262</v>
       </c>
@@ -4168,7 +4178,7 @@
         <v>2147483647</v>
       </c>
       <c r="E12">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -4192,7 +4202,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>267</v>
       </c>
@@ -4227,7 +4237,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>272</v>
       </c>
@@ -4262,7 +4272,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>276</v>
       </c>
@@ -4300,7 +4310,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>282</v>
       </c>
@@ -4338,7 +4348,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>287</v>
       </c>
@@ -4376,7 +4386,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>293</v>
       </c>
@@ -4414,7 +4424,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>297</v>
       </c>
@@ -4452,7 +4462,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>301</v>
       </c>
@@ -4490,7 +4500,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>306</v>
       </c>
@@ -4528,7 +4538,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>311</v>
       </c>
@@ -4566,7 +4576,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>315</v>
       </c>
@@ -4604,7 +4614,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>319</v>
       </c>
@@ -4642,7 +4652,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>323</v>
       </c>
@@ -4686,11 +4696,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q69"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>89</v>
       </c>
@@ -4719,7 +4729,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D2" t="s">
         <v>213</v>
       </c>
@@ -4760,7 +4770,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>332</v>
       </c>
@@ -4801,7 +4811,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>337</v>
       </c>
@@ -4842,7 +4852,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>340</v>
       </c>
@@ -4883,7 +4893,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>344</v>
       </c>
@@ -4924,7 +4934,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>347</v>
       </c>
@@ -4965,7 +4975,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>350</v>
       </c>
@@ -5006,7 +5016,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>353</v>
       </c>
@@ -5047,7 +5057,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>356</v>
       </c>
@@ -5088,7 +5098,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>359</v>
       </c>
@@ -5129,7 +5139,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>363</v>
       </c>
@@ -5170,7 +5180,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>366</v>
       </c>
@@ -5211,7 +5221,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>370</v>
       </c>
@@ -5252,7 +5262,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>375</v>
       </c>
@@ -5290,7 +5300,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>379</v>
       </c>
@@ -5331,7 +5341,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>383</v>
       </c>
@@ -5372,7 +5382,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>386</v>
       </c>
@@ -5416,7 +5426,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>391</v>
       </c>
@@ -5460,7 +5470,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>395</v>
       </c>
@@ -5501,7 +5511,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>399</v>
       </c>
@@ -5542,7 +5552,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>402</v>
       </c>
@@ -5583,7 +5593,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>405</v>
       </c>
@@ -5624,7 +5634,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>251</v>
       </c>
@@ -5641,7 +5651,7 @@
         <v>70000</v>
       </c>
       <c r="F24">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5668,7 +5678,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>256</v>
       </c>
@@ -5685,7 +5695,7 @@
         <v>2147483647</v>
       </c>
       <c r="F25">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5712,7 +5722,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>261</v>
       </c>
@@ -5729,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5756,7 +5766,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>265</v>
       </c>
@@ -5773,7 +5783,7 @@
         <v>2147483647</v>
       </c>
       <c r="F27">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5800,7 +5810,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>271</v>
       </c>
@@ -5844,7 +5854,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>275</v>
       </c>
@@ -5885,7 +5895,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>280</v>
       </c>
@@ -5929,7 +5939,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>285</v>
       </c>
@@ -5973,7 +5983,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>418</v>
       </c>
@@ -6017,7 +6027,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>422</v>
       </c>
@@ -6058,7 +6068,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>290</v>
       </c>
@@ -6102,7 +6112,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>305</v>
       </c>
@@ -6146,7 +6156,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>310</v>
       </c>
@@ -6190,7 +6200,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>326</v>
       </c>
@@ -6234,7 +6244,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>431</v>
       </c>
@@ -6278,7 +6288,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>435</v>
       </c>
@@ -6322,7 +6332,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>439</v>
       </c>
@@ -6366,7 +6376,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>443</v>
       </c>
@@ -6410,7 +6420,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>447</v>
       </c>
@@ -6454,7 +6464,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>452</v>
       </c>
@@ -6498,7 +6508,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>456</v>
       </c>
@@ -6542,7 +6552,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>460</v>
       </c>
@@ -6586,13 +6596,16 @@
         <v>292</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>464</v>
       </c>
       <c r="B46" t="s">
         <v>465</v>
       </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
       <c r="D46">
         <v>0</v>
       </c>
@@ -6627,7 +6640,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>468</v>
       </c>
@@ -6671,7 +6684,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>472</v>
       </c>
@@ -6715,7 +6728,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>476</v>
       </c>
@@ -6759,7 +6772,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>480</v>
       </c>
@@ -6800,7 +6813,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>483</v>
       </c>
@@ -6841,7 +6854,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>486</v>
       </c>
@@ -6882,7 +6895,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>489</v>
       </c>
@@ -6923,7 +6936,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>492</v>
       </c>
@@ -6964,7 +6977,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>496</v>
       </c>
@@ -7005,7 +7018,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>499</v>
       </c>
@@ -7046,7 +7059,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>502</v>
       </c>
@@ -7087,7 +7100,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>505</v>
       </c>
@@ -7128,7 +7141,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>508</v>
       </c>
@@ -7169,7 +7182,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>511</v>
       </c>
@@ -7210,7 +7223,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>515</v>
       </c>
@@ -7251,7 +7264,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>518</v>
       </c>
@@ -7292,7 +7305,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>521</v>
       </c>
@@ -7336,7 +7349,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>527</v>
       </c>
@@ -7380,7 +7393,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>531</v>
       </c>
@@ -7424,7 +7437,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>535</v>
       </c>
@@ -7468,7 +7481,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>539</v>
       </c>
@@ -7512,7 +7525,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>543</v>
       </c>
@@ -7556,7 +7569,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>546</v>
       </c>
@@ -7606,11 +7619,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>89</v>
       </c>
@@ -7636,7 +7649,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F2" t="s">
         <v>96</v>
       </c>
@@ -7659,11 +7672,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>556</v>
       </c>

--- a/data/profiles/minimal_1547.xlsx
+++ b/data/profiles/minimal_1547.xlsx
@@ -4660,10 +4660,10 @@
         <v>324</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -6211,10 +6211,10 @@
         <v>2</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -6229,7 +6229,7 @@
         <v>325</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="s">
         <v>323</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -6346,7 +6346,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -6786,10 +6786,10 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>100</v>
+        <v>70000</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6824,10 +6824,10 @@
         <v>3</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E51">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -6865,10 +6865,10 @@
         <v>3</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E52">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -6909,10 +6909,10 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -6950,10 +6950,10 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -6991,10 +6991,10 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7032,10 +7032,10 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7073,10 +7073,10 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7114,10 +7114,10 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7155,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -7193,13 +7193,13 @@
         <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E60">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E61">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -7275,13 +7275,13 @@
         <v>1</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E62">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -7319,10 +7319,10 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -7363,10 +7363,10 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -7407,10 +7407,10 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -7492,10 +7492,10 @@
         <v>2</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E67">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -7536,10 +7536,10 @@
         <v>2</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E68">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -7580,10 +7580,10 @@
         <v>2</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E69">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F69">
         <v>1</v>
